--- a/api/clv2/xlsx/fr/Currency.xlsx
+++ b/api/clv2/xlsx/fr/Currency.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="311">
   <si>
     <t>code</t>
   </si>
@@ -34,15 +34,27 @@
     <t>status</t>
   </si>
   <si>
+    <t>ADP</t>
+  </si>
+  <si>
+    <t>withdrawn</t>
+  </si>
+  <si>
     <t>AED</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>AFA</t>
+  </si>
+  <si>
     <t>AFN</t>
   </si>
   <si>
+    <t>ALK</t>
+  </si>
+  <si>
     <t>ALL</t>
   </si>
   <si>
@@ -55,18 +67,48 @@
     <t>AOA</t>
   </si>
   <si>
+    <t>AOK</t>
+  </si>
+  <si>
+    <t>AON</t>
+  </si>
+  <si>
+    <t>AOR</t>
+  </si>
+  <si>
+    <t>ARA</t>
+  </si>
+  <si>
+    <t>ARP</t>
+  </si>
+  <si>
     <t>ARS</t>
   </si>
   <si>
+    <t>ARY</t>
+  </si>
+  <si>
+    <t>ATS</t>
+  </si>
+  <si>
     <t>AUD</t>
   </si>
   <si>
     <t>AWG</t>
   </si>
   <si>
+    <t>AYM</t>
+  </si>
+  <si>
+    <t>AZM</t>
+  </si>
+  <si>
     <t>AZN</t>
   </si>
   <si>
+    <t>BAD</t>
+  </si>
+  <si>
     <t>BAM</t>
   </si>
   <si>
@@ -76,6 +118,24 @@
     <t>BDT</t>
   </si>
   <si>
+    <t>BEC</t>
+  </si>
+  <si>
+    <t>BEF</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>BGJ</t>
+  </si>
+  <si>
+    <t>BGK</t>
+  </si>
+  <si>
+    <t>BGL</t>
+  </si>
+  <si>
     <t>BGN</t>
   </si>
   <si>
@@ -94,30 +154,51 @@
     <t>BOB</t>
   </si>
   <si>
+    <t>BOP</t>
+  </si>
+  <si>
     <t>BOV</t>
   </si>
   <si>
+    <t>BRB</t>
+  </si>
+  <si>
+    <t>BRC</t>
+  </si>
+  <si>
+    <t>BRE</t>
+  </si>
+  <si>
     <t>BRL</t>
   </si>
   <si>
+    <t>BRN</t>
+  </si>
+  <si>
+    <t>BRR</t>
+  </si>
+  <si>
     <t>BSD</t>
   </si>
   <si>
     <t>BTN</t>
   </si>
   <si>
+    <t>BUK</t>
+  </si>
+  <si>
     <t>BWP</t>
   </si>
   <si>
+    <t>BYB</t>
+  </si>
+  <si>
+    <t>BYN</t>
+  </si>
+  <si>
     <t>BYR</t>
   </si>
   <si>
-    <t>withdrawn</t>
-  </si>
-  <si>
-    <t>BYN</t>
-  </si>
-  <si>
     <t>BZD</t>
   </si>
   <si>
@@ -127,9 +208,18 @@
     <t>CDF</t>
   </si>
   <si>
+    <t>CHC</t>
+  </si>
+  <si>
+    <t>CHE</t>
+  </si>
+  <si>
     <t>CHF</t>
   </si>
   <si>
+    <t>CHW</t>
+  </si>
+  <si>
     <t>CLF</t>
   </si>
   <si>
@@ -148,6 +238,15 @@
     <t>CRC</t>
   </si>
   <si>
+    <t>CSD</t>
+  </si>
+  <si>
+    <t>CSJ</t>
+  </si>
+  <si>
+    <t>CSK</t>
+  </si>
+  <si>
     <t>CUC</t>
   </si>
   <si>
@@ -157,9 +256,18 @@
     <t>CVE</t>
   </si>
   <si>
+    <t>CYP</t>
+  </si>
+  <si>
     <t>CZK</t>
   </si>
   <si>
+    <t>DDM</t>
+  </si>
+  <si>
+    <t>DEM</t>
+  </si>
+  <si>
     <t>DJF</t>
   </si>
   <si>
@@ -172,6 +280,12 @@
     <t>DZD</t>
   </si>
   <si>
+    <t>ECS</t>
+  </si>
+  <si>
+    <t>ECV</t>
+  </si>
+  <si>
     <t>EEK</t>
   </si>
   <si>
@@ -181,24 +295,48 @@
     <t>ERN</t>
   </si>
   <si>
+    <t>ESA</t>
+  </si>
+  <si>
+    <t>ESB</t>
+  </si>
+  <si>
+    <t>ESP</t>
+  </si>
+  <si>
     <t>ETB</t>
   </si>
   <si>
     <t>EUR</t>
   </si>
   <si>
+    <t>FIM</t>
+  </si>
+  <si>
     <t>FJD</t>
   </si>
   <si>
     <t>FKP</t>
   </si>
   <si>
+    <t>FRF</t>
+  </si>
+  <si>
     <t>GBP</t>
   </si>
   <si>
+    <t>GEK</t>
+  </si>
+  <si>
     <t>GEL</t>
   </si>
   <si>
+    <t>GHC</t>
+  </si>
+  <si>
+    <t>GHP</t>
+  </si>
+  <si>
     <t>GHS</t>
   </si>
   <si>
@@ -208,12 +346,30 @@
     <t>GMD</t>
   </si>
   <si>
+    <t>GNE</t>
+  </si>
+  <si>
     <t>GNF</t>
   </si>
   <si>
+    <t>GNS</t>
+  </si>
+  <si>
+    <t>GQE</t>
+  </si>
+  <si>
+    <t>GRD</t>
+  </si>
+  <si>
     <t>GTQ</t>
   </si>
   <si>
+    <t>GWE</t>
+  </si>
+  <si>
+    <t>GWP</t>
+  </si>
+  <si>
     <t>GYD</t>
   </si>
   <si>
@@ -223,6 +379,9 @@
     <t>HNL</t>
   </si>
   <si>
+    <t>HRD</t>
+  </si>
+  <si>
     <t>HRK</t>
   </si>
   <si>
@@ -235,6 +394,15 @@
     <t>IDR</t>
   </si>
   <si>
+    <t>IEP</t>
+  </si>
+  <si>
+    <t>ILP</t>
+  </si>
+  <si>
+    <t>ILR</t>
+  </si>
+  <si>
     <t>ILS</t>
   </si>
   <si>
@@ -247,9 +415,15 @@
     <t>IRR</t>
   </si>
   <si>
+    <t>ISJ</t>
+  </si>
+  <si>
     <t>ISK</t>
   </si>
   <si>
+    <t>ITL</t>
+  </si>
+  <si>
     <t>JMD</t>
   </si>
   <si>
@@ -286,6 +460,9 @@
     <t>KZT</t>
   </si>
   <si>
+    <t>LAJ</t>
+  </si>
+  <si>
     <t>LAK</t>
   </si>
   <si>
@@ -301,12 +478,30 @@
     <t>LSL</t>
   </si>
   <si>
+    <t>LSM</t>
+  </si>
+  <si>
     <t>LTL</t>
   </si>
   <si>
+    <t>LTT</t>
+  </si>
+  <si>
+    <t>LUC</t>
+  </si>
+  <si>
+    <t>LUF</t>
+  </si>
+  <si>
+    <t>LUL</t>
+  </si>
+  <si>
     <t>LVL</t>
   </si>
   <si>
+    <t>LVR</t>
+  </si>
+  <si>
     <t>LYD</t>
   </si>
   <si>
@@ -319,9 +514,15 @@
     <t>MGA</t>
   </si>
   <si>
+    <t>MGF</t>
+  </si>
+  <si>
     <t>MKD</t>
   </si>
   <si>
+    <t>MLF</t>
+  </si>
+  <si>
     <t>MMK</t>
   </si>
   <si>
@@ -337,9 +538,18 @@
     <t>MRU</t>
   </si>
   <si>
+    <t>MTL</t>
+  </si>
+  <si>
+    <t>MTP</t>
+  </si>
+  <si>
     <t>MUR</t>
   </si>
   <si>
+    <t>MVQ</t>
+  </si>
+  <si>
     <t>MVR</t>
   </si>
   <si>
@@ -349,12 +559,21 @@
     <t>MXN</t>
   </si>
   <si>
+    <t>MXP</t>
+  </si>
+  <si>
     <t>MXV</t>
   </si>
   <si>
     <t>MYR</t>
   </si>
   <si>
+    <t>MZE</t>
+  </si>
+  <si>
+    <t>MZM</t>
+  </si>
+  <si>
     <t>MZN</t>
   </si>
   <si>
@@ -364,9 +583,15 @@
     <t>NGN</t>
   </si>
   <si>
+    <t>NIC</t>
+  </si>
+  <si>
     <t>NIO</t>
   </si>
   <si>
+    <t>NLG</t>
+  </si>
+  <si>
     <t>NOK</t>
   </si>
   <si>
@@ -382,9 +607,18 @@
     <t>PAB</t>
   </si>
   <si>
+    <t>PEH</t>
+  </si>
+  <si>
+    <t>PEI</t>
+  </si>
+  <si>
     <t>PEN</t>
   </si>
   <si>
+    <t>PES</t>
+  </si>
+  <si>
     <t>PGK</t>
   </si>
   <si>
@@ -397,12 +631,27 @@
     <t>PLN</t>
   </si>
   <si>
+    <t>PLZ</t>
+  </si>
+  <si>
+    <t>PTE</t>
+  </si>
+  <si>
     <t>PYG</t>
   </si>
   <si>
     <t>QAR</t>
   </si>
   <si>
+    <t>RHD</t>
+  </si>
+  <si>
+    <t>ROK</t>
+  </si>
+  <si>
+    <t>ROL</t>
+  </si>
+  <si>
     <t>RON</t>
   </si>
   <si>
@@ -412,6 +661,9 @@
     <t>RUB</t>
   </si>
   <si>
+    <t>RUR</t>
+  </si>
+  <si>
     <t>RWF</t>
   </si>
   <si>
@@ -424,9 +676,15 @@
     <t>SCR</t>
   </si>
   <si>
+    <t>SDD</t>
+  </si>
+  <si>
     <t>SDG</t>
   </si>
   <si>
+    <t>SDP</t>
+  </si>
+  <si>
     <t>SEK</t>
   </si>
   <si>
@@ -436,24 +694,36 @@
     <t>SHP</t>
   </si>
   <si>
+    <t>SIT</t>
+  </si>
+  <si>
+    <t>SKK</t>
+  </si>
+  <si>
     <t>SLL</t>
   </si>
   <si>
     <t>SOS</t>
   </si>
   <si>
+    <t>SRD</t>
+  </si>
+  <si>
+    <t>SRG</t>
+  </si>
+  <si>
     <t>SSP</t>
   </si>
   <si>
-    <t>SRD</t>
-  </si>
-  <si>
     <t>STD</t>
   </si>
   <si>
     <t>STN</t>
   </si>
   <si>
+    <t>SUR</t>
+  </si>
+  <si>
     <t>SVC</t>
   </si>
   <si>
@@ -466,9 +736,15 @@
     <t>THB</t>
   </si>
   <si>
+    <t>TJR</t>
+  </si>
+  <si>
     <t>TJS</t>
   </si>
   <si>
+    <t>TMM</t>
+  </si>
+  <si>
     <t>TMT</t>
   </si>
   <si>
@@ -478,6 +754,12 @@
     <t>TOP</t>
   </si>
   <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>TRL</t>
+  </si>
+  <si>
     <t>TRY</t>
   </si>
   <si>
@@ -493,6 +775,15 @@
     <t>UAH</t>
   </si>
   <si>
+    <t>UAK</t>
+  </si>
+  <si>
+    <t>UGS</t>
+  </si>
+  <si>
+    <t>UGW</t>
+  </si>
+  <si>
     <t>UGX</t>
   </si>
   <si>
@@ -508,18 +799,33 @@
     <t>UYI</t>
   </si>
   <si>
+    <t>UYN</t>
+  </si>
+  <si>
+    <t>UYP</t>
+  </si>
+  <si>
     <t>UYU</t>
   </si>
   <si>
+    <t>UYW</t>
+  </si>
+  <si>
     <t>UZS</t>
   </si>
   <si>
+    <t>VEB</t>
+  </si>
+  <si>
     <t>VEF</t>
   </si>
   <si>
     <t>VES</t>
   </si>
   <si>
+    <t>VNC</t>
+  </si>
+  <si>
     <t>VND</t>
   </si>
   <si>
@@ -532,6 +838,24 @@
     <t>XAF</t>
   </si>
   <si>
+    <t>XAG</t>
+  </si>
+  <si>
+    <t>XAU</t>
+  </si>
+  <si>
+    <t>XBA</t>
+  </si>
+  <si>
+    <t>XBB</t>
+  </si>
+  <si>
+    <t>XBC</t>
+  </si>
+  <si>
+    <t>XBD</t>
+  </si>
+  <si>
     <t>XBT</t>
   </si>
   <si>
@@ -541,15 +865,60 @@
     <t>XDR</t>
   </si>
   <si>
+    <t>XEU</t>
+  </si>
+  <si>
+    <t>XFO</t>
+  </si>
+  <si>
+    <t>XFU</t>
+  </si>
+  <si>
     <t>XOF</t>
   </si>
   <si>
+    <t>XPD</t>
+  </si>
+  <si>
     <t>XPF</t>
   </si>
   <si>
+    <t>XPT</t>
+  </si>
+  <si>
+    <t>XRE</t>
+  </si>
+  <si>
+    <t>XSU</t>
+  </si>
+  <si>
+    <t>XTS</t>
+  </si>
+  <si>
+    <t>XUA</t>
+  </si>
+  <si>
+    <t>XXX</t>
+  </si>
+  <si>
+    <t>YDD</t>
+  </si>
+  <si>
     <t>YER</t>
   </si>
   <si>
+    <t>YUD</t>
+  </si>
+  <si>
+    <t>YUM</t>
+  </si>
+  <si>
+    <t>YUN</t>
+  </si>
+  <si>
+    <t>ZAL</t>
+  </si>
+  <si>
     <t>ZAR</t>
   </si>
   <si>
@@ -559,7 +928,25 @@
     <t>ZMW</t>
   </si>
   <si>
+    <t>ZRN</t>
+  </si>
+  <si>
+    <t>ZRZ</t>
+  </si>
+  <si>
+    <t>ZWC</t>
+  </si>
+  <si>
+    <t>ZWD</t>
+  </si>
+  <si>
     <t>ZWL</t>
+  </si>
+  <si>
+    <t>ZWN</t>
+  </si>
+  <si>
+    <t>ZWR</t>
   </si>
 </sst>
 </file>
@@ -891,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F175"/>
+  <dimension ref="A1:F304"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -927,12 +1314,12 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>7</v>
@@ -940,15 +1327,15 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
         <v>7</v>
@@ -956,23 +1343,23 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
         <v>7</v>
@@ -980,15 +1367,15 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
         <v>7</v>
@@ -996,7 +1383,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
         <v>7</v>
@@ -1004,7 +1391,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
         <v>7</v>
@@ -1012,7 +1399,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F14" t="s">
         <v>7</v>
@@ -1020,7 +1407,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F15" t="s">
         <v>7</v>
@@ -1028,15 +1415,15 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F16" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s">
         <v>7</v>
@@ -1044,7 +1431,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F18" t="s">
         <v>7</v>
@@ -1052,23 +1439,23 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F19" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F20" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F21" t="s">
         <v>7</v>
@@ -1076,7 +1463,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F22" t="s">
         <v>7</v>
@@ -1084,15 +1471,15 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F23" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F24" t="s">
         <v>7</v>
@@ -1100,18 +1487,18 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F25" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F26" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1119,7 +1506,7 @@
         <v>33</v>
       </c>
       <c r="F27" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1175,7 +1562,7 @@
         <v>40</v>
       </c>
       <c r="F34" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1183,7 +1570,7 @@
         <v>41</v>
       </c>
       <c r="F35" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1191,7 +1578,7 @@
         <v>42</v>
       </c>
       <c r="F36" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1199,7 +1586,7 @@
         <v>43</v>
       </c>
       <c r="F37" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1207,7 +1594,7 @@
         <v>44</v>
       </c>
       <c r="F38" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1215,7 +1602,7 @@
         <v>45</v>
       </c>
       <c r="F39" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1231,7 +1618,7 @@
         <v>47</v>
       </c>
       <c r="F41" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1263,7 +1650,7 @@
         <v>51</v>
       </c>
       <c r="F45" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1271,7 +1658,7 @@
         <v>52</v>
       </c>
       <c r="F46" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -1287,7 +1674,7 @@
         <v>54</v>
       </c>
       <c r="F48" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1295,7 +1682,7 @@
         <v>55</v>
       </c>
       <c r="F49" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -1311,7 +1698,7 @@
         <v>57</v>
       </c>
       <c r="F51" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -1327,7 +1714,7 @@
         <v>59</v>
       </c>
       <c r="F53" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -1343,7 +1730,7 @@
         <v>61</v>
       </c>
       <c r="F55" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -1351,7 +1738,7 @@
         <v>62</v>
       </c>
       <c r="F56" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -1359,7 +1746,7 @@
         <v>63</v>
       </c>
       <c r="F57" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -1375,7 +1762,7 @@
         <v>65</v>
       </c>
       <c r="F59" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -1383,7 +1770,7 @@
         <v>66</v>
       </c>
       <c r="F60" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -1391,7 +1778,7 @@
         <v>67</v>
       </c>
       <c r="F61" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -1399,7 +1786,7 @@
         <v>68</v>
       </c>
       <c r="F62" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -1407,7 +1794,7 @@
         <v>69</v>
       </c>
       <c r="F63" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -1415,7 +1802,7 @@
         <v>70</v>
       </c>
       <c r="F64" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -1423,7 +1810,7 @@
         <v>71</v>
       </c>
       <c r="F65" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -1431,7 +1818,7 @@
         <v>72</v>
       </c>
       <c r="F66" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -1439,7 +1826,7 @@
         <v>73</v>
       </c>
       <c r="F67" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -1471,7 +1858,7 @@
         <v>77</v>
       </c>
       <c r="F71" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -1479,7 +1866,7 @@
         <v>78</v>
       </c>
       <c r="F72" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -1487,7 +1874,7 @@
         <v>79</v>
       </c>
       <c r="F73" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -1503,7 +1890,7 @@
         <v>81</v>
       </c>
       <c r="F75" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -1527,7 +1914,7 @@
         <v>84</v>
       </c>
       <c r="F78" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -1535,7 +1922,7 @@
         <v>85</v>
       </c>
       <c r="F79" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -1543,7 +1930,7 @@
         <v>86</v>
       </c>
       <c r="F80" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -1551,7 +1938,7 @@
         <v>87</v>
       </c>
       <c r="F81" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -1583,7 +1970,7 @@
         <v>91</v>
       </c>
       <c r="F85" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -1591,7 +1978,7 @@
         <v>92</v>
       </c>
       <c r="F86" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -1615,7 +2002,7 @@
         <v>95</v>
       </c>
       <c r="F89" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -1623,7 +2010,7 @@
         <v>96</v>
       </c>
       <c r="F90" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -1647,7 +2034,7 @@
         <v>99</v>
       </c>
       <c r="F93" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -1655,7 +2042,7 @@
         <v>100</v>
       </c>
       <c r="F94" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -1671,7 +2058,7 @@
         <v>102</v>
       </c>
       <c r="F96" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -1687,7 +2074,7 @@
         <v>104</v>
       </c>
       <c r="F98" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -1695,7 +2082,7 @@
         <v>105</v>
       </c>
       <c r="F99" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -1711,7 +2098,7 @@
         <v>107</v>
       </c>
       <c r="F101" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -1719,7 +2106,7 @@
         <v>108</v>
       </c>
       <c r="F102" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -1727,7 +2114,7 @@
         <v>109</v>
       </c>
       <c r="F103" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -1743,7 +2130,7 @@
         <v>111</v>
       </c>
       <c r="F105" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -1775,7 +2162,7 @@
         <v>115</v>
       </c>
       <c r="F109" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -1799,7 +2186,7 @@
         <v>118</v>
       </c>
       <c r="F112" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -1807,7 +2194,7 @@
         <v>119</v>
       </c>
       <c r="F113" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -1815,7 +2202,7 @@
         <v>120</v>
       </c>
       <c r="F114" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -1839,7 +2226,7 @@
         <v>123</v>
       </c>
       <c r="F117" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -1847,7 +2234,7 @@
         <v>124</v>
       </c>
       <c r="F118" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -1887,7 +2274,7 @@
         <v>129</v>
       </c>
       <c r="F123" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -1895,7 +2282,7 @@
         <v>130</v>
       </c>
       <c r="F124" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -1903,7 +2290,7 @@
         <v>131</v>
       </c>
       <c r="F125" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -1911,7 +2298,7 @@
         <v>132</v>
       </c>
       <c r="F126" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -1927,7 +2314,7 @@
         <v>134</v>
       </c>
       <c r="F128" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -1943,7 +2330,7 @@
         <v>136</v>
       </c>
       <c r="F130" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -1951,7 +2338,7 @@
         <v>137</v>
       </c>
       <c r="F131" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -1959,7 +2346,7 @@
         <v>138</v>
       </c>
       <c r="F132" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -1967,7 +2354,7 @@
         <v>139</v>
       </c>
       <c r="F133" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -1975,7 +2362,7 @@
         <v>140</v>
       </c>
       <c r="F134" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -1983,7 +2370,7 @@
         <v>141</v>
       </c>
       <c r="F135" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -1991,7 +2378,7 @@
         <v>142</v>
       </c>
       <c r="F136" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -1999,7 +2386,7 @@
         <v>143</v>
       </c>
       <c r="F137" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -2007,7 +2394,7 @@
         <v>144</v>
       </c>
       <c r="F138" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -2015,7 +2402,7 @@
         <v>145</v>
       </c>
       <c r="F139" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -2023,7 +2410,7 @@
         <v>146</v>
       </c>
       <c r="F140" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -2031,7 +2418,7 @@
         <v>147</v>
       </c>
       <c r="F141" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -2047,7 +2434,7 @@
         <v>149</v>
       </c>
       <c r="F143" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -2055,7 +2442,7 @@
         <v>150</v>
       </c>
       <c r="F144" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -2063,7 +2450,7 @@
         <v>151</v>
       </c>
       <c r="F145" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -2071,7 +2458,7 @@
         <v>152</v>
       </c>
       <c r="F146" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -2079,7 +2466,7 @@
         <v>153</v>
       </c>
       <c r="F147" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -2151,7 +2538,7 @@
         <v>162</v>
       </c>
       <c r="F156" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -2159,7 +2546,7 @@
         <v>163</v>
       </c>
       <c r="F157" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -2167,7 +2554,7 @@
         <v>164</v>
       </c>
       <c r="F158" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -2175,7 +2562,7 @@
         <v>165</v>
       </c>
       <c r="F159" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -2183,7 +2570,7 @@
         <v>166</v>
       </c>
       <c r="F160" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -2191,7 +2578,7 @@
         <v>167</v>
       </c>
       <c r="F161" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -2207,7 +2594,7 @@
         <v>169</v>
       </c>
       <c r="F163" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -2215,7 +2602,7 @@
         <v>170</v>
       </c>
       <c r="F164" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -2223,7 +2610,7 @@
         <v>171</v>
       </c>
       <c r="F165" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -2239,7 +2626,7 @@
         <v>173</v>
       </c>
       <c r="F167" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -2263,7 +2650,7 @@
         <v>176</v>
       </c>
       <c r="F170" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -2279,7 +2666,7 @@
         <v>178</v>
       </c>
       <c r="F172" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -2287,7 +2674,7 @@
         <v>179</v>
       </c>
       <c r="F173" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -2295,7 +2682,7 @@
         <v>180</v>
       </c>
       <c r="F174" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -2303,6 +2690,1038 @@
         <v>181</v>
       </c>
       <c r="F175" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" t="s">
+        <v>182</v>
+      </c>
+      <c r="F176" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
+      <c r="A177" t="s">
+        <v>183</v>
+      </c>
+      <c r="F177" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178" t="s">
+        <v>184</v>
+      </c>
+      <c r="F178" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179" t="s">
+        <v>185</v>
+      </c>
+      <c r="F179" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180" t="s">
+        <v>186</v>
+      </c>
+      <c r="F180" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181" t="s">
+        <v>187</v>
+      </c>
+      <c r="F181" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" t="s">
+        <v>188</v>
+      </c>
+      <c r="F182" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="A183" t="s">
+        <v>189</v>
+      </c>
+      <c r="F183" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="A184" t="s">
+        <v>190</v>
+      </c>
+      <c r="F184" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="A185" t="s">
+        <v>191</v>
+      </c>
+      <c r="F185" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
+      <c r="A186" t="s">
+        <v>192</v>
+      </c>
+      <c r="F186" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="A187" t="s">
+        <v>193</v>
+      </c>
+      <c r="F187" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
+      <c r="A188" t="s">
+        <v>194</v>
+      </c>
+      <c r="F188" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
+      <c r="A189" t="s">
+        <v>195</v>
+      </c>
+      <c r="F189" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="A190" t="s">
+        <v>196</v>
+      </c>
+      <c r="F190" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="A191" t="s">
+        <v>197</v>
+      </c>
+      <c r="F191" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="A192" t="s">
+        <v>198</v>
+      </c>
+      <c r="F192" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
+      <c r="A193" t="s">
+        <v>199</v>
+      </c>
+      <c r="F193" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" t="s">
+        <v>200</v>
+      </c>
+      <c r="F194" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" t="s">
+        <v>201</v>
+      </c>
+      <c r="F195" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196" t="s">
+        <v>202</v>
+      </c>
+      <c r="F196" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197" t="s">
+        <v>203</v>
+      </c>
+      <c r="F197" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198" t="s">
+        <v>204</v>
+      </c>
+      <c r="F198" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" t="s">
+        <v>205</v>
+      </c>
+      <c r="F199" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" t="s">
+        <v>206</v>
+      </c>
+      <c r="F200" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201" t="s">
+        <v>207</v>
+      </c>
+      <c r="F201" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" t="s">
+        <v>208</v>
+      </c>
+      <c r="F202" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" t="s">
+        <v>209</v>
+      </c>
+      <c r="F203" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" t="s">
+        <v>210</v>
+      </c>
+      <c r="F204" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" t="s">
+        <v>211</v>
+      </c>
+      <c r="F205" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" t="s">
+        <v>212</v>
+      </c>
+      <c r="F206" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207" t="s">
+        <v>213</v>
+      </c>
+      <c r="F207" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208" t="s">
+        <v>214</v>
+      </c>
+      <c r="F208" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209" t="s">
+        <v>215</v>
+      </c>
+      <c r="F209" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" t="s">
+        <v>216</v>
+      </c>
+      <c r="F210" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" t="s">
+        <v>217</v>
+      </c>
+      <c r="F211" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" t="s">
+        <v>218</v>
+      </c>
+      <c r="F212" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213" t="s">
+        <v>219</v>
+      </c>
+      <c r="F213" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214" t="s">
+        <v>220</v>
+      </c>
+      <c r="F214" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
+      <c r="A215" t="s">
+        <v>221</v>
+      </c>
+      <c r="F215" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
+      <c r="A216" t="s">
+        <v>222</v>
+      </c>
+      <c r="F216" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
+      <c r="A217" t="s">
+        <v>223</v>
+      </c>
+      <c r="F217" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
+      <c r="A218" t="s">
+        <v>224</v>
+      </c>
+      <c r="F218" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
+      <c r="A219" t="s">
+        <v>225</v>
+      </c>
+      <c r="F219" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
+      <c r="A220" t="s">
+        <v>226</v>
+      </c>
+      <c r="F220" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
+      <c r="A221" t="s">
+        <v>227</v>
+      </c>
+      <c r="F221" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
+      <c r="A222" t="s">
+        <v>228</v>
+      </c>
+      <c r="F222" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
+      <c r="A223" t="s">
+        <v>229</v>
+      </c>
+      <c r="F223" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
+      <c r="A224" t="s">
+        <v>230</v>
+      </c>
+      <c r="F224" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6">
+      <c r="A225" t="s">
+        <v>231</v>
+      </c>
+      <c r="F225" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
+      <c r="A226" t="s">
+        <v>232</v>
+      </c>
+      <c r="F226" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
+      <c r="A227" t="s">
+        <v>233</v>
+      </c>
+      <c r="F227" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
+      <c r="A228" t="s">
+        <v>234</v>
+      </c>
+      <c r="F228" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6">
+      <c r="A229" t="s">
+        <v>235</v>
+      </c>
+      <c r="F229" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
+      <c r="A230" t="s">
+        <v>236</v>
+      </c>
+      <c r="F230" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
+      <c r="A231" t="s">
+        <v>237</v>
+      </c>
+      <c r="F231" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
+      <c r="A232" t="s">
+        <v>238</v>
+      </c>
+      <c r="F232" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
+      <c r="A233" t="s">
+        <v>239</v>
+      </c>
+      <c r="F233" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
+      <c r="A234" t="s">
+        <v>240</v>
+      </c>
+      <c r="F234" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
+      <c r="A235" t="s">
+        <v>241</v>
+      </c>
+      <c r="F235" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
+      <c r="A236" t="s">
+        <v>242</v>
+      </c>
+      <c r="F236" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
+      <c r="A237" t="s">
+        <v>243</v>
+      </c>
+      <c r="F237" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
+      <c r="A238" t="s">
+        <v>244</v>
+      </c>
+      <c r="F238" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
+      <c r="A239" t="s">
+        <v>245</v>
+      </c>
+      <c r="F239" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
+      <c r="A240" t="s">
+        <v>246</v>
+      </c>
+      <c r="F240" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
+      <c r="A241" t="s">
+        <v>247</v>
+      </c>
+      <c r="F241" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
+      <c r="A242" t="s">
+        <v>248</v>
+      </c>
+      <c r="F242" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
+      <c r="A243" t="s">
+        <v>249</v>
+      </c>
+      <c r="F243" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
+      <c r="A244" t="s">
+        <v>250</v>
+      </c>
+      <c r="F244" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
+      <c r="A245" t="s">
+        <v>251</v>
+      </c>
+      <c r="F245" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
+      <c r="A246" t="s">
+        <v>252</v>
+      </c>
+      <c r="F246" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
+      <c r="A247" t="s">
+        <v>253</v>
+      </c>
+      <c r="F247" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
+      <c r="A248" t="s">
+        <v>254</v>
+      </c>
+      <c r="F248" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6">
+      <c r="A249" t="s">
+        <v>255</v>
+      </c>
+      <c r="F249" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
+      <c r="A250" t="s">
+        <v>256</v>
+      </c>
+      <c r="F250" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
+      <c r="A251" t="s">
+        <v>257</v>
+      </c>
+      <c r="F251" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
+      <c r="A252" t="s">
+        <v>258</v>
+      </c>
+      <c r="F252" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
+      <c r="A253" t="s">
+        <v>259</v>
+      </c>
+      <c r="F253" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6">
+      <c r="A254" t="s">
+        <v>260</v>
+      </c>
+      <c r="F254" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
+      <c r="A255" t="s">
+        <v>261</v>
+      </c>
+      <c r="F255" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6">
+      <c r="A256" t="s">
+        <v>262</v>
+      </c>
+      <c r="F256" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
+      <c r="A257" t="s">
+        <v>263</v>
+      </c>
+      <c r="F257" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
+      <c r="A258" t="s">
+        <v>264</v>
+      </c>
+      <c r="F258" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
+      <c r="A259" t="s">
+        <v>265</v>
+      </c>
+      <c r="F259" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
+      <c r="A260" t="s">
+        <v>266</v>
+      </c>
+      <c r="F260" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
+      <c r="A261" t="s">
+        <v>267</v>
+      </c>
+      <c r="F261" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
+      <c r="A262" t="s">
+        <v>268</v>
+      </c>
+      <c r="F262" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
+      <c r="A263" t="s">
+        <v>269</v>
+      </c>
+      <c r="F263" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
+      <c r="A264" t="s">
+        <v>270</v>
+      </c>
+      <c r="F264" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
+      <c r="A265" t="s">
+        <v>271</v>
+      </c>
+      <c r="F265" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
+      <c r="A266" t="s">
+        <v>272</v>
+      </c>
+      <c r="F266" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267" t="s">
+        <v>273</v>
+      </c>
+      <c r="F267" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
+      <c r="A268" t="s">
+        <v>274</v>
+      </c>
+      <c r="F268" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
+      <c r="A269" t="s">
+        <v>275</v>
+      </c>
+      <c r="F269" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
+      <c r="A270" t="s">
+        <v>276</v>
+      </c>
+      <c r="F270" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="A271" t="s">
+        <v>277</v>
+      </c>
+      <c r="F271" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
+      <c r="A272" t="s">
+        <v>278</v>
+      </c>
+      <c r="F272" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
+      <c r="A273" t="s">
+        <v>279</v>
+      </c>
+      <c r="F273" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274" t="s">
+        <v>280</v>
+      </c>
+      <c r="F274" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
+      <c r="A275" t="s">
+        <v>281</v>
+      </c>
+      <c r="F275" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
+      <c r="A276" t="s">
+        <v>282</v>
+      </c>
+      <c r="F276" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
+      <c r="A277" t="s">
+        <v>283</v>
+      </c>
+      <c r="F277" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
+      <c r="A278" t="s">
+        <v>284</v>
+      </c>
+      <c r="F278" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
+      <c r="A279" t="s">
+        <v>285</v>
+      </c>
+      <c r="F279" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
+      <c r="A280" t="s">
+        <v>286</v>
+      </c>
+      <c r="F280" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
+      <c r="A281" t="s">
+        <v>287</v>
+      </c>
+      <c r="F281" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
+      <c r="A282" t="s">
+        <v>288</v>
+      </c>
+      <c r="F282" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
+      <c r="A283" t="s">
+        <v>289</v>
+      </c>
+      <c r="F283" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
+      <c r="A284" t="s">
+        <v>290</v>
+      </c>
+      <c r="F284" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
+      <c r="A285" t="s">
+        <v>291</v>
+      </c>
+      <c r="F285" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="A286" t="s">
+        <v>292</v>
+      </c>
+      <c r="F286" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="A287" t="s">
+        <v>293</v>
+      </c>
+      <c r="F287" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
+      <c r="A288" t="s">
+        <v>294</v>
+      </c>
+      <c r="F288" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
+      <c r="A289" t="s">
+        <v>295</v>
+      </c>
+      <c r="F289" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
+      <c r="A290" t="s">
+        <v>296</v>
+      </c>
+      <c r="F290" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291" t="s">
+        <v>297</v>
+      </c>
+      <c r="F291" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
+      <c r="A292" t="s">
+        <v>298</v>
+      </c>
+      <c r="F292" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6">
+      <c r="A293" t="s">
+        <v>299</v>
+      </c>
+      <c r="F293" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
+      <c r="A294" t="s">
+        <v>300</v>
+      </c>
+      <c r="F294" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
+      <c r="A295" t="s">
+        <v>301</v>
+      </c>
+      <c r="F295" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
+      <c r="A296" t="s">
+        <v>302</v>
+      </c>
+      <c r="F296" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
+      <c r="A297" t="s">
+        <v>303</v>
+      </c>
+      <c r="F297" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
+      <c r="A298" t="s">
+        <v>304</v>
+      </c>
+      <c r="F298" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
+      <c r="A299" t="s">
+        <v>305</v>
+      </c>
+      <c r="F299" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6">
+      <c r="A300" t="s">
+        <v>306</v>
+      </c>
+      <c r="F300" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
+      <c r="A301" t="s">
+        <v>307</v>
+      </c>
+      <c r="F301" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
+      <c r="A302" t="s">
+        <v>308</v>
+      </c>
+      <c r="F302" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
+      <c r="A303" t="s">
+        <v>309</v>
+      </c>
+      <c r="F303" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
+      <c r="A304" t="s">
+        <v>310</v>
+      </c>
+      <c r="F304" t="s">
         <v>7</v>
       </c>
     </row>

--- a/api/clv2/xlsx/fr/Currency.xlsx
+++ b/api/clv2/xlsx/fr/Currency.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="323">
   <si>
     <t>code</t>
   </si>
@@ -32,6 +32,42 @@
   </si>
   <si>
     <t>status</t>
+  </si>
+  <si>
+    <t>public-database</t>
+  </si>
+  <si>
+    <t>budget_alignment_guidance</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>global-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
   </si>
   <si>
     <t>ADP</t>
@@ -1278,10 +1314,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F304"/>
+  <dimension ref="A1:YP304"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:666">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1300,2429 +1336,4409 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>7</v>
+      </c>
+      <c r="R1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S1" t="s">
+        <v>7</v>
+      </c>
+      <c r="T1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U1" t="s">
+        <v>7</v>
+      </c>
+      <c r="V1" t="s">
+        <v>7</v>
+      </c>
+      <c r="W1" t="s">
+        <v>7</v>
+      </c>
+      <c r="X1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ER1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ES1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ID1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="II1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LT1" t="s">
+        <v>8</v>
+      </c>
+      <c r="LU1" t="s">
+        <v>9</v>
+      </c>
+      <c r="LV1" t="s">
+        <v>10</v>
+      </c>
+      <c r="LW1" t="s">
+        <v>11</v>
+      </c>
+      <c r="LX1" t="s">
+        <v>12</v>
+      </c>
+      <c r="LY1" t="s">
+        <v>13</v>
+      </c>
+      <c r="LZ1" t="s">
+        <v>14</v>
+      </c>
+      <c r="MA1" t="s">
+        <v>15</v>
+      </c>
+      <c r="MB1" t="s">
+        <v>16</v>
+      </c>
+      <c r="MC1" t="s">
+        <v>17</v>
+      </c>
+      <c r="MD1" t="s">
+        <v>6</v>
+      </c>
+      <c r="ME1" t="s">
+        <v>7</v>
+      </c>
+      <c r="MF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="MG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="MH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="MI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="MJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="MK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ML1" t="s">
+        <v>7</v>
+      </c>
+      <c r="MM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="MN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="MO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="MP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="MQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="MR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="MS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="MT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="MU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="MV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="MW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="MX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="MY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="MZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ND1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="NZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ON1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="OZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="PZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="QZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="RZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ST1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="SZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="TZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="US1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="UZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="VZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="WZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="XZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="YA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="YB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="YC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="YD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="YE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="YF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="YG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="YH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="YI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="YJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="YK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="YL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="YM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="YN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="YO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="YP1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:666">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:666">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:666">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:666">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:666">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:666">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:666">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:666">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:666">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:666">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:666">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:666">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:666">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:666">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:666">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F17" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F19" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F21" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F22" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F23" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F24" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F25" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F26" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F28" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F30" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F31" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F32" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F33" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F34" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F35" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F36" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F37" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="F38" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F39" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F40" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="F41" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F42" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F43" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="F44" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F45" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="F46" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F47" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="F48" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F49" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="F50" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="F51" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="F52" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F53" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F54" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="F55" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="F56" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F57" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F58" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="F59" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="F60" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="F61" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="F62" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F63" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="F64" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="F65" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="F66" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F67" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="F68" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F69" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="F70" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="F71" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F72" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="F73" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F74" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="F75" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="F76" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F77" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="F78" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="F79" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F80" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="F81" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F82" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="F83" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="F84" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F85" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="F86" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="F87" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="F88" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="F89" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="F90" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="F91" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="F92" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="F93" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="F94" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="F95" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="F96" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="F97" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F98" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="F99" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="F100" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="F101" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="F102" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="F103" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F104" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="F105" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="F106" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="F107" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F108" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="F109" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="F110" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="F111" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="F112" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F113" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F114" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="F115" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F116" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="F117" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="F118" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="F119" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F120" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="F121" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F122" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="F123" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F124" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="F125" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="F126" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F127" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="F128" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="F129" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="F130" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="F131" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="F132" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="F133" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="F134" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="F135" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="F136" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="F137" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="F138" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="F139" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="F140" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F141" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="F142" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="F143" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="F144" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="F145" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="F146" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="F147" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="F148" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="F149" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="F150" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F151" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="F152" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="F153" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="F154" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="F155" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="F156" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="F157" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="F158" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="F159" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F160" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="F161" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="F162" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="F163" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="F164" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="F165" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="F166" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="F167" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="F168" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="F169" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="F170" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="F171" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F172" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="F173" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="F174" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="F175" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="F176" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="F177" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="F178" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="F179" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="F180" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="F181" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="F182" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="F183" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="F184" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="F185" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="F186" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="F187" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="F188" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="F189" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="F190" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="F191" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="F192" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="F193" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="F194" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="F195" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="F196" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="F197" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="F198" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="F199" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="F200" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="F201" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="F202" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="F203" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="F204" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="F205" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="F206" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="207" spans="1:6">
       <c r="A207" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="F207" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="208" spans="1:6">
       <c r="A208" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="F208" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="209" spans="1:6">
       <c r="A209" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="F209" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="210" spans="1:6">
       <c r="A210" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F210" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="F211" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="F212" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="F213" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F214" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="F215" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="216" spans="1:6">
       <c r="A216" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="F216" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F217" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="F218" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F219" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="220" spans="1:6">
       <c r="A220" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="F220" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="221" spans="1:6">
       <c r="A221" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="F221" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="222" spans="1:6">
       <c r="A222" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="F222" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="223" spans="1:6">
       <c r="A223" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="F223" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="224" spans="1:6">
       <c r="A224" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="F224" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="225" spans="1:6">
       <c r="A225" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="F225" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="226" spans="1:6">
       <c r="A226" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="F226" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="227" spans="1:6">
       <c r="A227" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="F227" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="228" spans="1:6">
       <c r="A228" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="F228" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="229" spans="1:6">
       <c r="A229" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="F229" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="230" spans="1:6">
       <c r="A230" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="F230" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="231" spans="1:6">
       <c r="A231" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="F231" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="232" spans="1:6">
       <c r="A232" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="F232" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="233" spans="1:6">
       <c r="A233" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="F233" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="234" spans="1:6">
       <c r="A234" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="F234" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="235" spans="1:6">
       <c r="A235" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="F235" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="236" spans="1:6">
       <c r="A236" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="F236" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="237" spans="1:6">
       <c r="A237" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="F237" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="238" spans="1:6">
       <c r="A238" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="F238" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="239" spans="1:6">
       <c r="A239" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="F239" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="240" spans="1:6">
       <c r="A240" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="F240" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="241" spans="1:6">
       <c r="A241" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="F241" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="242" spans="1:6">
       <c r="A242" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="F242" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="243" spans="1:6">
       <c r="A243" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="F243" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="244" spans="1:6">
       <c r="A244" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="F244" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="245" spans="1:6">
       <c r="A245" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="F245" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="246" spans="1:6">
       <c r="A246" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="F246" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="247" spans="1:6">
       <c r="A247" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="F247" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="248" spans="1:6">
       <c r="A248" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="F248" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="249" spans="1:6">
       <c r="A249" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="F249" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="250" spans="1:6">
       <c r="A250" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="F250" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="251" spans="1:6">
       <c r="A251" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="F251" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="252" spans="1:6">
       <c r="A252" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="F252" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="253" spans="1:6">
       <c r="A253" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F253" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="F254" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="255" spans="1:6">
       <c r="A255" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="F255" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="256" spans="1:6">
       <c r="A256" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="F256" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="257" spans="1:6">
       <c r="A257" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="F257" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="258" spans="1:6">
       <c r="A258" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="F258" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="259" spans="1:6">
       <c r="A259" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="F259" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="260" spans="1:6">
       <c r="A260" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="F260" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="261" spans="1:6">
       <c r="A261" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="F261" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="262" spans="1:6">
       <c r="A262" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="F262" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="263" spans="1:6">
       <c r="A263" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="F263" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="264" spans="1:6">
       <c r="A264" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="F264" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="265" spans="1:6">
       <c r="A265" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="F265" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="266" spans="1:6">
       <c r="A266" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="F266" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="267" spans="1:6">
       <c r="A267" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="F267" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="268" spans="1:6">
       <c r="A268" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="F268" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="269" spans="1:6">
       <c r="A269" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="F269" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="270" spans="1:6">
       <c r="A270" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="F270" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="271" spans="1:6">
       <c r="A271" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="F271" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="272" spans="1:6">
       <c r="A272" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="F272" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="273" spans="1:6">
       <c r="A273" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="F273" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="274" spans="1:6">
       <c r="A274" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="F274" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="275" spans="1:6">
       <c r="A275" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="F275" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="276" spans="1:6">
       <c r="A276" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="F276" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="277" spans="1:6">
       <c r="A277" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F277" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="278" spans="1:6">
       <c r="A278" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="F278" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="279" spans="1:6">
       <c r="A279" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="F279" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="280" spans="1:6">
       <c r="A280" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="F280" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="281" spans="1:6">
       <c r="A281" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="F281" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="282" spans="1:6">
       <c r="A282" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="F282" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="283" spans="1:6">
       <c r="A283" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="F283" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="284" spans="1:6">
       <c r="A284" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="F284" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="285" spans="1:6">
       <c r="A285" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="F285" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="286" spans="1:6">
       <c r="A286" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="F286" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="287" spans="1:6">
       <c r="A287" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="F287" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="288" spans="1:6">
       <c r="A288" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="F288" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="289" spans="1:6">
       <c r="A289" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="F289" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="290" spans="1:6">
       <c r="A290" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="F290" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="291" spans="1:6">
       <c r="A291" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="F291" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="292" spans="1:6">
       <c r="A292" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="F292" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="293" spans="1:6">
       <c r="A293" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="F293" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="294" spans="1:6">
       <c r="A294" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="F294" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="295" spans="1:6">
       <c r="A295" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="F295" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="296" spans="1:6">
       <c r="A296" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="F296" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="297" spans="1:6">
       <c r="A297" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F297" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="298" spans="1:6">
       <c r="A298" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="F298" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="299" spans="1:6">
       <c r="A299" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="F299" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="300" spans="1:6">
       <c r="A300" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="F300" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="301" spans="1:6">
       <c r="A301" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="F301" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="302" spans="1:6">
       <c r="A302" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="F302" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="303" spans="1:6">
       <c r="A303" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="F303" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="304" spans="1:6">
       <c r="A304" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="F304" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/api/clv2/xlsx/fr/Currency.xlsx
+++ b/api/clv2/xlsx/fr/Currency.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>iso-alpha-3-code</t>
   </si>
   <si>
     <t>region-code</t>
   </si>
   <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
+    <t>global-name</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
     <t>sub-region-name</t>
   </si>
   <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>global-name</t>
-  </si>
-  <si>
     <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
-    <t>global-code</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
   </si>
   <si>
     <t>ADP</t>

--- a/api/clv2/xlsx/fr/Currency.xlsx
+++ b/api/clv2/xlsx/fr/Currency.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>intermediate-region-name</t>
   </si>
   <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
     <t>sub-region-code</t>
   </si>
   <si>
-    <t>global-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
-  </si>
-  <si>
     <t>global-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
   </si>
   <si>
     <t>ADP</t>

--- a/api/clv2/xlsx/fr/Currency.xlsx
+++ b/api/clv2/xlsx/fr/Currency.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>global-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
     <t>global-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
-  </si>
-  <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>global-name</t>
   </si>
   <si>
     <t>ADP</t>

--- a/api/clv2/xlsx/fr/Currency.xlsx
+++ b/api/clv2/xlsx/fr/Currency.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>global-name</t>
   </si>
   <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
     <t>region-code</t>
   </si>
   <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
     <t>region-name</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
-  </si>
-  <si>
-    <t>global-code</t>
   </si>
   <si>
     <t>ADP</t>

--- a/api/clv2/xlsx/fr/Currency.xlsx
+++ b/api/clv2/xlsx/fr/Currency.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>global-name</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
     <t>intermediate-region-name</t>
   </si>
   <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
     <t>intermediate-region-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>global-code</t>
-  </si>
-  <si>
-    <t>global-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
   </si>
   <si>
     <t>ADP</t>

--- a/api/clv2/xlsx/fr/Currency.xlsx
+++ b/api/clv2/xlsx/fr/Currency.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
     <t>global-name</t>
   </si>
   <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
     <t>sub-region-code</t>
   </si>
   <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
     <t>global-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
   </si>
   <si>
     <t>ADP</t>

--- a/api/clv2/xlsx/fr/Currency.xlsx
+++ b/api/clv2/xlsx/fr/Currency.xlsx
@@ -43,31 +43,31 @@
     <t>iso-alpha-3-code</t>
   </si>
   <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
     <t>intermediate-region-code</t>
   </si>
   <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>intermediate-region-name</t>
   </si>
   <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
     <t>global-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>global-code</t>
   </si>
   <si>
     <t>ADP</t>

--- a/api/clv2/xlsx/fr/Currency.xlsx
+++ b/api/clv2/xlsx/fr/Currency.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="311">
   <si>
     <t>code</t>
   </si>
@@ -32,42 +32,6 @@
   </si>
   <si>
     <t>status</t>
-  </si>
-  <si>
-    <t>public-database</t>
-  </si>
-  <si>
-    <t>budget_alignment_guidance</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
-  </si>
-  <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>global-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>global-name</t>
   </si>
   <si>
     <t>ADP</t>
@@ -1314,10 +1278,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:YP304"/>
+  <dimension ref="A1:F304"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:666">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1336,4409 +1300,2429 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" t="s">
-        <v>7</v>
-      </c>
-      <c r="O1" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>7</v>
-      </c>
-      <c r="R1" t="s">
-        <v>7</v>
-      </c>
-      <c r="S1" t="s">
-        <v>7</v>
-      </c>
-      <c r="T1" t="s">
-        <v>7</v>
-      </c>
-      <c r="U1" t="s">
-        <v>7</v>
-      </c>
-      <c r="V1" t="s">
-        <v>7</v>
-      </c>
-      <c r="W1" t="s">
-        <v>7</v>
-      </c>
-      <c r="X1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="ED1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="ER1" t="s">
-        <v>7</v>
-      </c>
-      <c r="ES1" t="s">
-        <v>7</v>
-      </c>
-      <c r="ET1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="ID1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="II1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LT1" t="s">
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="LU1" t="s">
-        <v>9</v>
-      </c>
-      <c r="LV1" t="s">
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="LW1" t="s">
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="LX1" t="s">
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="LY1" t="s">
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="LZ1" t="s">
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="MA1" t="s">
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
         <v>15</v>
       </c>
-      <c r="MB1" t="s">
+      <c r="F9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="MC1" t="s">
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
         <v>17</v>
       </c>
-      <c r="MD1" t="s">
-        <v>6</v>
-      </c>
-      <c r="ME1" t="s">
-        <v>7</v>
-      </c>
-      <c r="MF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="MG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="MH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="MI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="MJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="MK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="ML1" t="s">
-        <v>7</v>
-      </c>
-      <c r="MM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="MN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="MO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="MP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="MQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="MR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="MS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="MT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="MU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="MV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="MW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="MX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="MY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="MZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="ND1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="NZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="ON1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="OZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="PZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="QZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="RZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="ST1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="SZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="TZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="US1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="UZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="VZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="WZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="XZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="YA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="YB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="YC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="YD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="YE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="YF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="YG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="YH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="YI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="YJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="YK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="YL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="YM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="YN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="YO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="YP1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:666">
-      <c r="A2" t="s">
+      <c r="F11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:666">
-      <c r="A3" t="s">
+      <c r="F13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:666">
-      <c r="A4" t="s">
+      <c r="F15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
         <v>22</v>
       </c>
-      <c r="F4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:666">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:666">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:666">
-      <c r="A7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:666">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:666">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:666">
-      <c r="A10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:666">
-      <c r="A11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:666">
-      <c r="A12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:666">
-      <c r="A13" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:666">
-      <c r="A14" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:666">
-      <c r="A15" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:666">
-      <c r="A16" t="s">
-        <v>34</v>
-      </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F18" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F19" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F20" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F21" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F22" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="F23" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F24" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="F25" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F26" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="F27" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F28" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="F29" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F30" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F31" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F32" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F33" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="F34" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F35" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F36" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="F37" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F38" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F39" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="F40" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F41" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F42" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F43" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="F44" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="F45" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F46" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="F47" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="F48" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F49" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="F50" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="F51" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F52" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F53" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="F54" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="F55" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="F56" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="F57" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="F58" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F59" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F60" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="F61" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="F62" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="F63" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="F64" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="F65" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="F66" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="F67" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F68" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="F69" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F70" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="F71" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="F72" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="F73" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="F74" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="F75" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F76" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="F77" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="F78" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="F79" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="F80" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="F81" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F82" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="F83" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="F84" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="F85" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="F86" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="F87" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F88" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="F89" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="F90" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="F91" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="F92" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="F93" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="F94" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="F95" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="F96" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F97" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="F98" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="F99" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="F100" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="F101" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="F102" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="F103" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="F104" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="F105" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F106" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="F107" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="F108" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="F109" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="F110" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="F111" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="F112" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="F113" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F114" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="F115" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="F116" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="F117" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F118" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="F119" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="F120" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="F121" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F122" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="F123" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="F124" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="F125" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="F126" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="F127" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="F128" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="F129" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="F130" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="F131" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="F132" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="F133" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="F134" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="F135" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="F136" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F137" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="F138" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="F139" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="F140" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="F141" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="F142" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="F143" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="F144" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="F145" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="F146" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="F147" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="F148" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="F149" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="F150" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="F151" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="F152" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="F153" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="F154" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="F155" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="F156" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="F157" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="F158" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="F159" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="F160" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="F161" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="F162" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="F163" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="F164" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="F165" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="F166" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="F167" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="F168" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="F169" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="F170" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="F171" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="F172" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="F173" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="F174" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="F175" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="F176" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="F177" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="F178" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="F179" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="F180" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="F181" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="F182" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="F183" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="F184" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="F185" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="F186" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="F187" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="F188" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="F189" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="F190" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="F191" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F192" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="F193" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="F194" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F195" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="F196" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="F197" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F198" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="F199" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="F200" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="F201" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="F202" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="F203" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F204" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="F205" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="F206" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="207" spans="1:6">
       <c r="A207" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F207" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="208" spans="1:6">
       <c r="A208" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F208" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="209" spans="1:6">
       <c r="A209" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F209" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="210" spans="1:6">
       <c r="A210" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F210" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F211" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="F212" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="F213" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F214" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="F215" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="216" spans="1:6">
       <c r="A216" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="F216" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="F217" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="F218" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F219" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="220" spans="1:6">
       <c r="A220" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="F220" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="221" spans="1:6">
       <c r="A221" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="F221" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="222" spans="1:6">
       <c r="A222" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="F222" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="223" spans="1:6">
       <c r="A223" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F223" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="224" spans="1:6">
       <c r="A224" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F224" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="225" spans="1:6">
       <c r="A225" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F225" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="226" spans="1:6">
       <c r="A226" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="F226" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="227" spans="1:6">
       <c r="A227" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="F227" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="228" spans="1:6">
       <c r="A228" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="F228" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="229" spans="1:6">
       <c r="A229" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="F229" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="230" spans="1:6">
       <c r="A230" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="F230" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="231" spans="1:6">
       <c r="A231" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F231" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="232" spans="1:6">
       <c r="A232" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F232" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="233" spans="1:6">
       <c r="A233" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="F233" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="234" spans="1:6">
       <c r="A234" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="F234" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="235" spans="1:6">
       <c r="A235" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F235" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="236" spans="1:6">
       <c r="A236" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="F236" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="237" spans="1:6">
       <c r="A237" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="F237" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="238" spans="1:6">
       <c r="A238" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="F238" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="239" spans="1:6">
       <c r="A239" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="F239" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="240" spans="1:6">
       <c r="A240" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="F240" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="241" spans="1:6">
       <c r="A241" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="F241" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="242" spans="1:6">
       <c r="A242" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="F242" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="243" spans="1:6">
       <c r="A243" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="F243" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="244" spans="1:6">
       <c r="A244" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="F244" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="245" spans="1:6">
       <c r="A245" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="F245" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="246" spans="1:6">
       <c r="A246" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="F246" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="247" spans="1:6">
       <c r="A247" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="F247" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="248" spans="1:6">
       <c r="A248" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="F248" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="249" spans="1:6">
       <c r="A249" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="F249" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="250" spans="1:6">
       <c r="A250" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="F250" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="251" spans="1:6">
       <c r="A251" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="F251" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="252" spans="1:6">
       <c r="A252" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="F252" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="253" spans="1:6">
       <c r="A253" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="F253" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="F254" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="255" spans="1:6">
       <c r="A255" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="F255" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="256" spans="1:6">
       <c r="A256" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="F256" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="257" spans="1:6">
       <c r="A257" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="F257" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="258" spans="1:6">
       <c r="A258" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="F258" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="259" spans="1:6">
       <c r="A259" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="F259" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="260" spans="1:6">
       <c r="A260" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="F260" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="261" spans="1:6">
       <c r="A261" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="F261" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="262" spans="1:6">
       <c r="A262" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="F262" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="263" spans="1:6">
       <c r="A263" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="F263" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="264" spans="1:6">
       <c r="A264" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="F264" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="265" spans="1:6">
       <c r="A265" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F265" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="266" spans="1:6">
       <c r="A266" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="F266" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="267" spans="1:6">
       <c r="A267" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="F267" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="268" spans="1:6">
       <c r="A268" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="F268" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="269" spans="1:6">
       <c r="A269" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="F269" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="270" spans="1:6">
       <c r="A270" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="F270" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="271" spans="1:6">
       <c r="A271" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="F271" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="272" spans="1:6">
       <c r="A272" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F272" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="273" spans="1:6">
       <c r="A273" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="F273" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="274" spans="1:6">
       <c r="A274" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="F274" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="275" spans="1:6">
       <c r="A275" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="F275" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="276" spans="1:6">
       <c r="A276" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="F276" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="277" spans="1:6">
       <c r="A277" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="F277" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="278" spans="1:6">
       <c r="A278" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="F278" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="279" spans="1:6">
       <c r="A279" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="F279" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="280" spans="1:6">
       <c r="A280" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="F280" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="281" spans="1:6">
       <c r="A281" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="F281" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="282" spans="1:6">
       <c r="A282" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="F282" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="283" spans="1:6">
       <c r="A283" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="F283" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="284" spans="1:6">
       <c r="A284" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="F284" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="285" spans="1:6">
       <c r="A285" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="F285" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="286" spans="1:6">
       <c r="A286" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="F286" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="287" spans="1:6">
       <c r="A287" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="F287" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="288" spans="1:6">
       <c r="A288" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="F288" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="289" spans="1:6">
       <c r="A289" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="F289" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="290" spans="1:6">
       <c r="A290" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="F290" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="291" spans="1:6">
       <c r="A291" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="F291" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="292" spans="1:6">
       <c r="A292" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="F292" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="293" spans="1:6">
       <c r="A293" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="F293" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="294" spans="1:6">
       <c r="A294" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="F294" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="295" spans="1:6">
       <c r="A295" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="F295" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="296" spans="1:6">
       <c r="A296" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="F296" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="297" spans="1:6">
       <c r="A297" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F297" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="298" spans="1:6">
       <c r="A298" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="F298" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="299" spans="1:6">
       <c r="A299" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="F299" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="300" spans="1:6">
       <c r="A300" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="F300" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="301" spans="1:6">
       <c r="A301" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="F301" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="302" spans="1:6">
       <c r="A302" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="F302" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="303" spans="1:6">
       <c r="A303" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="F303" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="304" spans="1:6">
       <c r="A304" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="F304" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
